--- a/VanHanhCD1/wwwroot/templates/BMVH_LUYENCOC_QGTH2.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_LUYENCOC_QGTH2.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\LC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86189F7-ADB7-4372-9EF0-5BE42DFB7AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -62,48 +61,6 @@
   </si>
   <si>
     <t>Kí hiệu</t>
-  </si>
-  <si>
-    <t>DONG_DC_PSB1</t>
-  </si>
-  <si>
-    <t>DONG_DC_PSB2</t>
-  </si>
-  <si>
-    <t>DONG_DC_PSB3</t>
-  </si>
-  <si>
-    <t>PI1501AM</t>
-  </si>
-  <si>
-    <t>FI1501AM</t>
-  </si>
-  <si>
-    <t>TI1501AM</t>
-  </si>
-  <si>
-    <t>DONG_DC_LSB1</t>
-  </si>
-  <si>
-    <t>DONG_DC_LSB2</t>
-  </si>
-  <si>
-    <t>DONG_DC_LSB3</t>
-  </si>
-  <si>
-    <t>FI1502AM</t>
-  </si>
-  <si>
-    <t>TI1502AM</t>
-  </si>
-  <si>
-    <t>DONG_DC_GSB1</t>
-  </si>
-  <si>
-    <t>DONG_DC_GSB2</t>
-  </si>
-  <si>
-    <t>DONG_DC_GSB3</t>
   </si>
   <si>
     <t>SỔ THEO DÕI THÔNG SỐ VẬN HÀNH ĐIỀU KHIỂN TRUNG TÂM CDQ1</t>
@@ -204,11 +161,53 @@
   <si>
     <t>SỔ THEO DÕI THÔNG SỐ VẬN HÀNH THIẾT BỊ CDQ2 130 TẤN/H</t>
   </si>
+  <si>
+    <t>QGTH2_RUNGGOISAU</t>
+  </si>
+  <si>
+    <t>QGTH2_U</t>
+  </si>
+  <si>
+    <t>QGTH2_V</t>
+  </si>
+  <si>
+    <t>QGTH2_W</t>
+  </si>
+  <si>
+    <t>CDQ2_TOCDOQUAT</t>
+  </si>
+  <si>
+    <t>QGTH2_DONGDIEN</t>
+  </si>
+  <si>
+    <t>CDQ2_RADAR</t>
+  </si>
+  <si>
+    <t>CDQ2_LB1</t>
+  </si>
+  <si>
+    <t>CDQ2_LB2</t>
+  </si>
+  <si>
+    <t>QGTH2_RUNGGOITRC</t>
+  </si>
+  <si>
+    <t>QGTH2_NDGOITRC</t>
+  </si>
+  <si>
+    <t>QGTH2_NDGOISAU</t>
+  </si>
+  <si>
+    <t>QGTH2_NDBITRC</t>
+  </si>
+  <si>
+    <t>QGTH1_NDVBSAU</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
@@ -1307,7 +1306,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA29"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1576,7 +1575,7 @@
       <c r="X1" s="11"/>
       <c r="Y1" s="11"/>
       <c r="Z1" s="7" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -1585,7 +1584,7 @@
       <c r="X2" s="12"/>
       <c r="Y2" s="12"/>
       <c r="Z2" s="7" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:27" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -1594,7 +1593,7 @@
     </row>
     <row r="4" spans="1:27" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -1624,11 +1623,11 @@
     </row>
     <row r="5" spans="1:27" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="26" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D5" s="26"/>
       <c r="E5" s="26"/>
@@ -1642,7 +1641,7 @@
       <c r="M5" s="26"/>
       <c r="N5" s="26"/>
       <c r="O5" s="26" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="P5" s="26"/>
       <c r="Q5" s="26"/>
@@ -1734,10 +1733,10 @@
     </row>
     <row r="7" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C7" s="20">
         <f>Sheet2!D6</f>
@@ -1840,7 +1839,7 @@
     <row r="8" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27"/>
       <c r="B8" s="19" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C8" s="20">
         <f>Sheet2!D7</f>
@@ -1943,7 +1942,7 @@
     <row r="9" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="27"/>
       <c r="B9" s="19" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C9" s="20">
         <f>Sheet2!D8</f>
@@ -2046,7 +2045,7 @@
     <row r="10" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27"/>
       <c r="B10" s="19" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C10" s="20">
         <f>Sheet2!D9</f>
@@ -2149,7 +2148,7 @@
     <row r="11" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="27"/>
       <c r="B11" s="19" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C11" s="20">
         <f>Sheet2!D10</f>
@@ -2252,7 +2251,7 @@
     <row r="12" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27"/>
       <c r="B12" s="19" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C12" s="20">
         <f>Sheet2!D11</f>
@@ -2355,7 +2354,7 @@
     <row r="13" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27"/>
       <c r="B13" s="19" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C13" s="20">
         <f>Sheet2!D12</f>
@@ -2458,7 +2457,7 @@
     <row r="14" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27"/>
       <c r="B14" s="19" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C14" s="20">
         <f>Sheet2!D13</f>
@@ -2561,7 +2560,7 @@
     <row r="15" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27"/>
       <c r="B15" s="19" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C15" s="20">
         <f>Sheet2!D14</f>
@@ -2664,7 +2663,7 @@
     <row r="16" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27"/>
       <c r="B16" s="19" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C16" s="20">
         <f>Sheet2!D15</f>
@@ -2767,7 +2766,7 @@
     <row r="17" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="27"/>
       <c r="B17" s="19" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C17" s="20">
         <f>Sheet2!D16</f>
@@ -2869,10 +2868,10 @@
     </row>
     <row r="18" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C18" s="20">
         <f>Sheet2!D17</f>
@@ -2975,7 +2974,7 @@
     <row r="19" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27"/>
       <c r="B19" s="19" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C19" s="20">
         <f>Sheet2!D18</f>
@@ -3078,7 +3077,7 @@
     <row r="20" spans="1:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="27"/>
       <c r="B20" s="19" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C20" s="21">
         <f>Sheet2!D19</f>
@@ -3180,11 +3179,11 @@
     </row>
     <row r="21" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="29" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
@@ -3198,7 +3197,7 @@
       <c r="M21" s="30"/>
       <c r="N21" s="31"/>
       <c r="O21" s="29" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="P21" s="30"/>
       <c r="Q21" s="30"/>
@@ -3217,7 +3216,7 @@
       <c r="A22" s="27"/>
       <c r="B22" s="28"/>
       <c r="C22" s="32" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="33"/>
@@ -3231,7 +3230,7 @@
       <c r="M22" s="33"/>
       <c r="N22" s="34"/>
       <c r="O22" s="32" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="P22" s="33"/>
       <c r="Q22" s="33"/>
@@ -3250,7 +3249,7 @@
       <c r="A23" s="27"/>
       <c r="B23" s="28"/>
       <c r="C23" s="35" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D23" s="36"/>
       <c r="E23" s="36"/>
@@ -3264,7 +3263,7 @@
       <c r="M23" s="36"/>
       <c r="N23" s="37"/>
       <c r="O23" s="35" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="P23" s="36"/>
       <c r="Q23" s="36"/>
@@ -3290,10 +3289,10 @@
     <row r="25" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="K25" s="14"/>
       <c r="L25" s="14" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="X25" s="14" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AA25" s="18"/>
     </row>
@@ -3357,13 +3356,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293588F-613F-4A05-8D7F-14CAABA20F0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
     <col min="2" max="2" width="60.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
     <col min="4" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="19" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="27" width="4.85546875" bestFit="1" customWidth="1"/>
@@ -3400,7 +3399,7 @@
       <c r="C2" s="46"/>
       <c r="D2" s="1"/>
       <c r="E2" s="41" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F2" s="41"/>
       <c r="G2" s="41"/>
@@ -3552,13 +3551,13 @@
     </row>
     <row r="6" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -3588,10 +3587,10 @@
     <row r="7" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="39"/>
       <c r="B7" s="19" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -3621,10 +3620,10 @@
     <row r="8" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="39"/>
       <c r="B8" s="19" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -3654,10 +3653,10 @@
     <row r="9" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="39"/>
       <c r="B9" s="19" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -3687,10 +3686,10 @@
     <row r="10" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="39"/>
       <c r="B10" s="19" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -3720,10 +3719,10 @@
     <row r="11" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="39"/>
       <c r="B11" s="19" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -3753,10 +3752,10 @@
     <row r="12" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="39"/>
       <c r="B12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>11</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -3786,10 +3785,10 @@
     <row r="13" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="39"/>
       <c r="B13" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>12</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -3819,10 +3818,10 @@
     <row r="14" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="39"/>
       <c r="B14" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -3852,10 +3851,10 @@
     <row r="15" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="39"/>
       <c r="B15" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -3885,10 +3884,10 @@
     <row r="16" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="40"/>
       <c r="B16" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>15</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -3918,10 +3917,10 @@
     <row r="17" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="38"/>
       <c r="B17" s="19" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -3951,10 +3950,10 @@
     <row r="18" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A18" s="39"/>
       <c r="B18" s="19" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -3984,10 +3983,10 @@
     <row r="19" spans="1:27" ht="33" x14ac:dyDescent="0.25">
       <c r="A19" s="40"/>
       <c r="B19" s="19" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
